--- a/implementation_evaluation_forms/015_healthcare_policy_implementation_evaluation--implementation_evaluation_forms.xlsx
+++ b/implementation_evaluation_forms/015_healthcare_policy_implementation_evaluation--implementation_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'effective',_'value':_'effective'}</t>
+          <t>effective</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Effective', 'value': 'effective'}</t>
+          <t>Effective</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'not_effective',_'value':_'not_effective'}</t>
+          <t>not_effective</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Not Effective', 'value': 'not_effective'}</t>
+          <t>Not Effective</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'quarterly',_'value':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Quarterly', 'value': 'quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'half-yearly',_'value':_'half_yearly'}</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Half-yearly', 'value': 'half_yearly'}</t>
+          <t>Half-yearly</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'yearly',_'value':_'yearly'}</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Yearly', 'value': 'yearly'}</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'sustainable',_'value':_'sustainable'}</t>
+          <t>sustainable</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Sustainable', 'value': 'sustainable'}</t>
+          <t>Sustainable</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'not_sustainable',_'value':_'not_sustainable'}</t>
+          <t>not_sustainable</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sustainable', 'value': 'not_sustainable'}</t>
+          <t>Not Sustainable</t>
         </is>
       </c>
     </row>
